--- a/dataset_t6_grouped/results2/G1/G1_T1912_W0046F0003T0006Z000C1N9_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T1912_W0046F0003T0006Z000C1N9_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>16.31173055048232</v>
+        <v>2.650656214453377</v>
       </c>
       <c r="D2" t="n">
-        <v>17.10164044146054</v>
+        <v>2.779016571737338</v>
       </c>
       <c r="E2" t="n">
-        <v>10.31783427583825</v>
+        <v>1.676648069823716</v>
       </c>
       <c r="F2" t="n">
-        <v>10.43581660966866</v>
+        <v>1.695820199071157</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>3.880697366463499</v>
+        <v>0.6306133220503186</v>
       </c>
       <c r="D3" t="n">
-        <v>3.533205826046263</v>
+        <v>0.5741459467325177</v>
       </c>
       <c r="E3" t="n">
-        <v>10.31783427583825</v>
+        <v>1.676648069823716</v>
       </c>
       <c r="F3" t="n">
-        <v>10.43581660966866</v>
+        <v>1.695820199071157</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>14.50598169619161</v>
+        <v>2.357222025631137</v>
       </c>
       <c r="D4" t="n">
-        <v>14.38821141473002</v>
+        <v>2.338084354893629</v>
       </c>
       <c r="E4" t="n">
-        <v>10.31783427583825</v>
+        <v>1.676648069823716</v>
       </c>
       <c r="F4" t="n">
-        <v>10.43581660966866</v>
+        <v>1.695820199071157</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>28.61772481751223</v>
+        <v>4.650380282845737</v>
       </c>
       <c r="D5" t="n">
-        <v>23.58582925288546</v>
+        <v>3.832697253593887</v>
       </c>
       <c r="E5" t="n">
-        <v>10.31783427583825</v>
+        <v>1.676648069823716</v>
       </c>
       <c r="F5" t="n">
-        <v>10.43581660966866</v>
+        <v>1.695820199071157</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>17.53410145140369</v>
+        <v>2.8492914858531</v>
       </c>
       <c r="D6" t="n">
-        <v>2.649455815771281</v>
+        <v>0.4305365700628332</v>
       </c>
       <c r="E6" t="n">
-        <v>10.31783427583825</v>
+        <v>1.676648069823716</v>
       </c>
       <c r="F6" t="n">
-        <v>10.43581660966866</v>
+        <v>1.695820199071157</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>40.24110417612527</v>
+        <v>6.539179428620357</v>
       </c>
       <c r="D7" t="n">
-        <v>34.88284165090236</v>
+        <v>5.668461768271635</v>
       </c>
       <c r="E7" t="n">
-        <v>10.31783427583825</v>
+        <v>1.676648069823716</v>
       </c>
       <c r="F7" t="n">
-        <v>10.43581660966866</v>
+        <v>1.695820199071157</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>16.27608452473695</v>
+        <v>2.644863735269755</v>
       </c>
       <c r="D8" t="n">
-        <v>4.407227159515198</v>
+        <v>0.7161744134212197</v>
       </c>
       <c r="E8" t="n">
-        <v>10.31783427583825</v>
+        <v>1.676648069823716</v>
       </c>
       <c r="F8" t="n">
-        <v>10.43581660966866</v>
+        <v>1.695820199071157</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>12.44326677686373</v>
+        <v>2.022030851240356</v>
       </c>
       <c r="D9" t="n">
-        <v>12.22171978275926</v>
+        <v>1.98602946469838</v>
       </c>
       <c r="E9" t="n">
-        <v>10.31783427583825</v>
+        <v>1.676648069823716</v>
       </c>
       <c r="F9" t="n">
-        <v>10.43581660966866</v>
+        <v>1.695820199071157</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
